--- a/Clase 7 - PowerBI/serie_salarios.xlsx
+++ b/Clase 7 - PowerBI/serie_salarios.xlsx
@@ -1,176 +1,197 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\OneDrive\Documentos\GitHub\curso_aset\Clase 7 - PowerBI\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ED2B30-F153-4FBD-870C-6FEC360EFBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="18000" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="serie_salarios" sheetId="1" r:id="rId1"/>
+    <sheet name="serie_salarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="serie_salarios_sexo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
-  <si>
-    <t>anio_trim</t>
-  </si>
-  <si>
-    <t>salario_promedio</t>
-  </si>
-  <si>
-    <t>2003T3</t>
-  </si>
-  <si>
-    <t>2003T4</t>
-  </si>
-  <si>
-    <t>2004T1</t>
-  </si>
-  <si>
-    <t>2004T2</t>
-  </si>
-  <si>
-    <t>2004T3</t>
-  </si>
-  <si>
-    <t>2004T4</t>
-  </si>
-  <si>
-    <t>2005T1</t>
-  </si>
-  <si>
-    <t>2005T2</t>
-  </si>
-  <si>
-    <t>2005T3</t>
-  </si>
-  <si>
-    <t>2005T4</t>
-  </si>
-  <si>
-    <t>2006T1</t>
-  </si>
-  <si>
-    <t>2006T2</t>
-  </si>
-  <si>
-    <t>2006T3</t>
-  </si>
-  <si>
-    <t>2006T4</t>
-  </si>
-  <si>
-    <t>2007T1</t>
-  </si>
-  <si>
-    <t>2016T2</t>
-  </si>
-  <si>
-    <t>2016T3</t>
-  </si>
-  <si>
-    <t>2016T4</t>
-  </si>
-  <si>
-    <t>2017T1</t>
-  </si>
-  <si>
-    <t>2017T2</t>
-  </si>
-  <si>
-    <t>2017T3</t>
-  </si>
-  <si>
-    <t>2017T4</t>
-  </si>
-  <si>
-    <t>2018T1</t>
-  </si>
-  <si>
-    <t>2018T2</t>
-  </si>
-  <si>
-    <t>2018T3</t>
-  </si>
-  <si>
-    <t>2018T4</t>
-  </si>
-  <si>
-    <t>2019T1</t>
-  </si>
-  <si>
-    <t>2019T2</t>
-  </si>
-  <si>
-    <t>2019T3</t>
-  </si>
-  <si>
-    <t>2019T4</t>
-  </si>
-  <si>
-    <t>2020T1</t>
-  </si>
-  <si>
-    <t>2020T2</t>
-  </si>
-  <si>
-    <t>2020T3</t>
-  </si>
-  <si>
-    <t>2020T4</t>
-  </si>
-  <si>
-    <t>2021T1</t>
-  </si>
-  <si>
-    <t>2021T2</t>
-  </si>
-  <si>
-    <t>2021T3</t>
-  </si>
-  <si>
-    <t>2021T4</t>
-  </si>
-  <si>
-    <t>2022T1</t>
-  </si>
-  <si>
-    <t>2022T2</t>
-  </si>
-  <si>
-    <t>2022T3</t>
-  </si>
-  <si>
-    <t>2022T4</t>
-  </si>
-  <si>
-    <t>2023T1</t>
-  </si>
-  <si>
-    <t>2023T2</t>
-  </si>
-  <si>
-    <t>2023T3</t>
-  </si>
-  <si>
-    <t>2023T4</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+  <si>
+    <t xml:space="preserve">anio_trim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salario_promedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2003T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2003T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2004T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2004T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2004T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2004T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2005T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2005T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2005T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2005T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2006T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2006T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2006T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2006T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CH04</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -199,23 +220,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -497,14 +508,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,376 +520,1661 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" t="n">
         <v>565.761397634216</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1">
-        <v>595.76490563156699</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" t="n">
+        <v>595.764905631567</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1">
-        <v>642.73606259343899</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="n">
+        <v>642.736062593439</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1">
-        <v>616.97097255891003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="n">
+        <v>616.97097255891</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
-        <v>637.76787347468201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="n">
+        <v>637.767873474682</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1">
-        <v>656.62526450220901</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="n">
+        <v>656.625264502209</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1">
-        <v>702.84308714864903</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="n">
+        <v>702.843087148649</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1">
-        <v>722.31191235593599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="n">
+        <v>722.311912355936</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" t="n">
         <v>781.428059494732</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1">
-        <v>821.28094573918895</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="n">
+        <v>821.280945739189</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="1">
-        <v>875.10889014095801</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" t="n">
+        <v>875.108890140958</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1">
-        <v>910.11622089347202</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" t="n">
+        <v>910.116220893472</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="1">
-        <v>956.83112281240403</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" t="n">
+        <v>956.831122812404</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" t="n">
         <v>1016.14691602007</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="1">
-        <v>1076.4947820272801</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="n">
+        <v>1076.49478202728</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="1">
-        <v>10466.952552487301</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="n">
+        <v>10466.9525524873</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" t="n">
         <v>11096.5102427973</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="1">
-        <v>11867.940129796099</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="n">
+        <v>11867.9401297961</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" t="n">
         <v>12760.2418005323</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="1">
-        <v>13374.356225618199</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="n">
+        <v>13374.3562256182</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" t="n">
         <v>14121.3370303705</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="1">
-        <v>14934.014422489599</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="n">
+        <v>14934.0144224896</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" t="n">
         <v>16293.2389591307</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="1">
-        <v>16827.993196193998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" t="n">
+        <v>16827.993196194</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="1">
-        <v>17538.413668847399</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="n">
+        <v>17538.4136688474</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="1">
-        <v>19298.654433489999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" t="n">
+        <v>19298.65443349</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="1">
-        <v>20639.944134060301</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="n">
+        <v>20639.9441340603</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="1">
-        <v>22658.422519169399</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B29" t="n">
+        <v>22658.4225191694</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" t="n">
         <v>25233.6075235477</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="1">
-        <v>27385.549774377701</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="n">
+        <v>27385.5497743777</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="1">
-        <v>30080.244754335199</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" t="n">
+        <v>30080.2447543352</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="1">
-        <v>34410.239339546199</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="n">
+        <v>34410.2393395462</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" t="n">
         <v>34206.1239920644</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="1">
-        <v>36245.662368296304</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="n">
+        <v>36245.6623682963</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="1">
-        <v>42294.125592946497</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" t="n">
+        <v>42294.1255929465</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="1">
-        <v>47231.521613881101</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" t="n">
+        <v>47231.5216138811</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="1">
-        <v>50849.023035388404</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" t="n">
+        <v>50849.0230353884</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="1">
-        <v>55822.989013652899</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B39" t="n">
+        <v>55822.9890136529</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="1">
-        <v>64755.321692945501</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B40" t="n">
+        <v>64755.3216929455</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="1">
-        <v>70678.195707761493</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B41" t="n">
+        <v>70678.1957077615</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="1">
-        <v>83310.462493696497</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" t="n">
+        <v>83310.4624936965</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" t="n">
         <v>100505.681530898</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="1">
-        <v>120972.88417941199</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" t="n">
+        <v>120972.884179412</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="1">
-        <v>149048.33096603499</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B45" t="n">
+        <v>149048.330966035</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="1">
-        <v>192286.56183178601</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B46" t="n">
+        <v>192286.561831786</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="1">
-        <v>262718.34792667301</v>
+      <c r="B47" t="n">
+        <v>262718.347926673</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" t="n">
+        <v>361445.403610194</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" t="n">
+        <v>501824.921941986</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" t="n">
+        <v>640469.802426309</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" t="n">
+        <v>744797.922227466</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" t="n">
+        <v>824242.335632727</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" t="n">
+        <v>924871.687760339</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" t="n">
+        <v>961755.859260497</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1082634.99726042</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>649.674557325366</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>472.821475183154</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>696.852970036845</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>479.160915508828</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>763.020894932401</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>494.465993276805</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>722.146604388634</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>491.785917620638</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>749.253345925197</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>503.638293683773</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>765.083792077908</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>522.377240877561</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>832.296631254744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>542.733171615024</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>850.258962807136</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>562.866330465977</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>911.75206311849</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>617.643506229815</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>957.886113882148</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>658.611359822693</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1014.80477423064</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>699.852906378943</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1066.32236236885</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>715.028356644203</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1110.0800892485</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>767.036029651675</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1175.20802778879</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>823.534383784748</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1242.58928665005</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>865.717815883974</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>11712.5611542576</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8903.31013504118</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>12369.1812192888</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>9551.57526727865</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>13355.8846879861</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>10076.2302114539</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>14403.7042672361</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>10729.7083465142</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>15110.4604557857</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>11222.5072766715</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>15909.9343447307</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>11908.9134318552</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>16718.8265727635</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>12744.6973329767</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>18332.4529518376</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>13747.3206733162</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>19007.1174848424</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>14192.1364120468</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>19884.9616855247</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="n">
+        <v>14666.987991573</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>27</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>21737.3824362795</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="n">
+        <v>16439.3844083703</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>23289.2508579214</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="n">
+        <v>17360.3905420052</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>25423.1567611292</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>29</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>19401.1341679686</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>28155.1075359382</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>21636.0718201449</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>30679.3440494331</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>31</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" t="n">
+        <v>23430.0572632012</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>33554.6266629898</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="n">
+        <v>25974.3449870538</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>38308.9185709823</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="n">
+        <v>29715.3216790519</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>34</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>37865.5481295286</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>34</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" t="n">
+        <v>29786.1297113205</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>39978.1324953235</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" t="n">
+        <v>31710.127410427</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>36</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>47129.6648039645</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>36</v>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="n">
+        <v>36051.9971286518</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>53746.9003199596</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" t="n">
+        <v>39231.8159419254</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="n">
+        <v>57693.9527936701</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>42652.9042158405</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>62093.2313932393</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>39</v>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="n">
+        <v>48182.598740812</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>73903.5318163196</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>53881.0369451427</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>80955.8441294113</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>41</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>58239.6133524753</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>42</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>92726.1821082482</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>42</v>
+      </c>
+      <c r="B84" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" t="n">
+        <v>72193.1151209946</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>43</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>111504.309008172</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>43</v>
+      </c>
+      <c r="B86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" t="n">
+        <v>87245.2492626397</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>44</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>136150.787976666</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>44</v>
+      </c>
+      <c r="B88" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" t="n">
+        <v>103205.120383169</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>45</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>169018.125872792</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>45</v>
+      </c>
+      <c r="B90" t="n">
+        <v>2</v>
+      </c>
+      <c r="C90" t="n">
+        <v>125630.877335662</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>46</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>212949.152109234</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>46</v>
+      </c>
+      <c r="B92" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" t="n">
+        <v>168063.794446135</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>47</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>294377.763482486</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>47</v>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="n">
+        <v>225451.692176048</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>48</v>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>407361.058859753</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>48</v>
+      </c>
+      <c r="B96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" t="n">
+        <v>306131.225888519</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>49</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>571060.690032561</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>49</v>
+      </c>
+      <c r="B98" t="n">
+        <v>2</v>
+      </c>
+      <c r="C98" t="n">
+        <v>419506.446226096</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>50</v>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="n">
+        <v>730567.060200998</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>50</v>
+      </c>
+      <c r="B100" t="n">
+        <v>2</v>
+      </c>
+      <c r="C100" t="n">
+        <v>535546.817380057</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>51</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="n">
+        <v>848652.316753855</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>51</v>
+      </c>
+      <c r="B102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" t="n">
+        <v>625023.543060782</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>52</v>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="n">
+        <v>940479.749928795</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>52</v>
+      </c>
+      <c r="B104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" t="n">
+        <v>683530.805620548</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>53</v>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1042816.60857793</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>53</v>
+      </c>
+      <c r="B106" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" t="n">
+        <v>781747.540656917</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>54</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1084774.78959865</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>54</v>
+      </c>
+      <c r="B108" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" t="n">
+        <v>811916.972064041</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>55</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1234427.45884561</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>55</v>
+      </c>
+      <c r="B110" t="n">
+        <v>2</v>
+      </c>
+      <c r="C110" t="n">
+        <v>903710.644789213</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>